--- a/it_forms/017_external_drive_unlock_request_form--it_forms.xlsx
+++ b/it_forms/017_external_drive_unlock_request_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>drive_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mac</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mac</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>drive_type_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>linux</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>john_doe</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jane_doe</t>
+          <t>jim_doe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jane Doe</t>
+          <t>Jim Doe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>external_drive_unlock_request_status_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jim_doe</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jim Doe</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>external_drive_unlock_request_status_choices</t>
+          <t>external_drive_unlock_request_priority_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>external_drive_unlock_request_priority_choices</t>
+          <t>external_drive_unlock_request_assigned_to_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1641,46 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>external_drive_unlock_request_assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>external_drive_unlock_request_assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
